--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848290</v>
+        <v>119848457</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,47 +815,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626227</v>
+        <v>626418</v>
       </c>
       <c r="R3" t="n">
-        <v>6897562</v>
+        <v>6897386</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1158,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848457</v>
+        <v>119848290</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,38 +1161,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626418</v>
+        <v>626227</v>
       </c>
       <c r="R6" t="n">
-        <v>6897386</v>
+        <v>6897562</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848186</v>
+        <v>119847868</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626224</v>
+        <v>626244</v>
       </c>
       <c r="R7" t="n">
-        <v>6897567</v>
+        <v>6897275</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119851155</v>
+        <v>119848186</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,51 +1398,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626302</v>
+        <v>626224</v>
       </c>
       <c r="R8" t="n">
-        <v>6897262</v>
+        <v>6897567</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847868</v>
+        <v>119851155</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,37 +1510,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626244</v>
+        <v>626302</v>
       </c>
       <c r="R9" t="n">
-        <v>6897275</v>
+        <v>6897262</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119847868</v>
+        <v>119848186</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626244</v>
+        <v>626224</v>
       </c>
       <c r="R7" t="n">
-        <v>6897275</v>
+        <v>6897567</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848186</v>
+        <v>119847868</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626224</v>
+        <v>626244</v>
       </c>
       <c r="R8" t="n">
-        <v>6897567</v>
+        <v>6897275</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848457</v>
+        <v>119847976</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,34 +819,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626418</v>
+        <v>626244</v>
       </c>
       <c r="R3" t="n">
-        <v>6897386</v>
+        <v>6897275</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1027,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847976</v>
+        <v>119848457</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,39 +1053,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626244</v>
+        <v>626418</v>
       </c>
       <c r="R5" t="n">
-        <v>6897275</v>
+        <v>6897386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848290</v>
+        <v>119848186</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,47 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626227</v>
+        <v>626224</v>
       </c>
       <c r="R6" t="n">
-        <v>6897562</v>
+        <v>6897567</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848186</v>
+        <v>119848290</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1273,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626224</v>
+        <v>626227</v>
       </c>
       <c r="R7" t="n">
-        <v>6897567</v>
+        <v>6897562</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847976</v>
+        <v>119847868</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,29 +819,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
@@ -883,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848312</v>
+        <v>119847976</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,34 +931,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626267</v>
+        <v>626244</v>
       </c>
       <c r="R4" t="n">
-        <v>6897527</v>
+        <v>6897275</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1005,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848186</v>
+        <v>119851155</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,37 +1165,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626224</v>
+        <v>626302</v>
       </c>
       <c r="R6" t="n">
-        <v>6897567</v>
+        <v>6897262</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848290</v>
+        <v>119848312</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,47 +1287,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626227</v>
+        <v>626267</v>
       </c>
       <c r="R7" t="n">
-        <v>6897562</v>
+        <v>6897527</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847868</v>
+        <v>119848186</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,21 +1403,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626244</v>
+        <v>626224</v>
       </c>
       <c r="R8" t="n">
-        <v>6897275</v>
+        <v>6897567</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119851155</v>
+        <v>119848290</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,55 +1511,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626302</v>
+        <v>626227</v>
       </c>
       <c r="R9" t="n">
-        <v>6897262</v>
+        <v>6897562</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848457</v>
+        <v>119851155</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,37 +1053,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626418</v>
+        <v>626302</v>
       </c>
       <c r="R5" t="n">
-        <v>6897386</v>
+        <v>6897262</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119851155</v>
+        <v>119848457</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,51 +1179,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626302</v>
+        <v>626418</v>
       </c>
       <c r="R6" t="n">
-        <v>6897262</v>
+        <v>6897386</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119851155</v>
+        <v>119848457</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,51 +1053,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626302</v>
+        <v>626418</v>
       </c>
       <c r="R5" t="n">
-        <v>6897262</v>
+        <v>6897386</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848457</v>
+        <v>119851155</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,37 +1165,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626418</v>
+        <v>626302</v>
       </c>
       <c r="R6" t="n">
-        <v>6897386</v>
+        <v>6897262</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119851155</v>
+        <v>119848312</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,51 +1165,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626302</v>
+        <v>626267</v>
       </c>
       <c r="R6" t="n">
-        <v>6897262</v>
+        <v>6897527</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848312</v>
+        <v>119848186</v>
       </c>
       <c r="B7" t="n">
         <v>90562</v>
@@ -1315,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626267</v>
+        <v>626224</v>
       </c>
       <c r="R7" t="n">
-        <v>6897527</v>
+        <v>6897567</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1350,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848186</v>
+        <v>119848290</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,38 +1385,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626224</v>
+        <v>626227</v>
       </c>
       <c r="R8" t="n">
-        <v>6897567</v>
+        <v>6897562</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1462,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,62 +1494,67 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848290</v>
+        <v>119851155</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dialog hos rapportör</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626227</v>
+        <v>626302</v>
       </c>
       <c r="R9" t="n">
-        <v>6897562</v>
+        <v>6897262</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,14 +1494,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119851155</v>
+        <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dialog hos rapportör</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1527,34 +1527,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626302</v>
+        <v>626204</v>
       </c>
       <c r="R9" t="n">
-        <v>6897262</v>
+        <v>6897437</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,19 +1575,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flerhundraårig tall med flera bohål av spillkråka, i olika åldrar, enstaka färska, flera äldre. Adult fågel hördes i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,6 +1606,134 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119851155</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dialog hos rapportör</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626302</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6897262</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dialog hos rapportör</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847868</v>
+        <v>119847976</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,24 +819,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
@@ -878,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +893,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847976</v>
+        <v>119847868</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,29 +941,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
@@ -995,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848457</v>
+        <v>119848186</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626418</v>
+        <v>626224</v>
       </c>
       <c r="R5" t="n">
-        <v>6897386</v>
+        <v>6897567</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,7 +1152,7 @@
         <v>119848312</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848186</v>
+        <v>119848457</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626224</v>
+        <v>626418</v>
       </c>
       <c r="R7" t="n">
-        <v>6897567</v>
+        <v>6897386</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,7 +1376,7 @@
         <v>119848290</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847868</v>
+        <v>119848312</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626244</v>
+        <v>626267</v>
       </c>
       <c r="R4" t="n">
-        <v>6897275</v>
+        <v>6897527</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848186</v>
+        <v>119848457</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626224</v>
+        <v>626418</v>
       </c>
       <c r="R5" t="n">
-        <v>6897567</v>
+        <v>6897386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848312</v>
+        <v>119848186</v>
       </c>
       <c r="B6" t="n">
         <v>90580</v>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626267</v>
+        <v>626224</v>
       </c>
       <c r="R6" t="n">
-        <v>6897527</v>
+        <v>6897567</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848457</v>
+        <v>119847868</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626418</v>
+        <v>626244</v>
       </c>
       <c r="R7" t="n">
-        <v>6897386</v>
+        <v>6897275</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847976</v>
+        <v>119848312</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,39 +819,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626244</v>
+        <v>626267</v>
       </c>
       <c r="R3" t="n">
-        <v>6897275</v>
+        <v>6897527</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,12 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848312</v>
+        <v>119847868</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +931,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626267</v>
+        <v>626244</v>
       </c>
       <c r="R4" t="n">
-        <v>6897527</v>
+        <v>6897275</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1010,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848457</v>
+        <v>119847976</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,34 +1043,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626418</v>
+        <v>626244</v>
       </c>
       <c r="R5" t="n">
-        <v>6897386</v>
+        <v>6897275</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848186</v>
+        <v>119848290</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1161,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626224</v>
+        <v>626227</v>
       </c>
       <c r="R6" t="n">
-        <v>6897567</v>
+        <v>6897562</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119847868</v>
+        <v>119848186</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626244</v>
+        <v>626224</v>
       </c>
       <c r="R7" t="n">
-        <v>6897275</v>
+        <v>6897567</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848290</v>
+        <v>119848457</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,47 +1394,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626227</v>
+        <v>626418</v>
       </c>
       <c r="R8" t="n">
-        <v>6897562</v>
+        <v>6897386</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119848312</v>
+        <v>119847868</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,21 +819,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626267</v>
+        <v>626244</v>
       </c>
       <c r="R3" t="n">
-        <v>6897527</v>
+        <v>6897275</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847868</v>
+        <v>119847976</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,24 +931,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
@@ -990,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1005,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847976</v>
+        <v>119848312</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,39 +1053,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626244</v>
+        <v>626267</v>
       </c>
       <c r="R5" t="n">
-        <v>6897275</v>
+        <v>6897527</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848290</v>
+        <v>119848457</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,47 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626227</v>
+        <v>626418</v>
       </c>
       <c r="R6" t="n">
-        <v>6897562</v>
+        <v>6897386</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1382,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848457</v>
+        <v>119848290</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,38 +1385,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626418</v>
+        <v>626227</v>
       </c>
       <c r="R8" t="n">
-        <v>6897386</v>
+        <v>6897562</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1512,11 +1512,6 @@
       <c r="E9" t="n">
         <v>100049</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,6 +1511,11 @@
       </c>
       <c r="E9" t="n">
         <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>119851155</v>
       </c>
       <c r="B10" t="n">
-        <v>57335</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>119851155</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>119851155</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1612,7 +1612,7 @@
         <v>119851155</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,12 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>120323464</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55593211</v>
+        <v>119848186</v>
       </c>
       <c r="B2" t="n">
-        <v>96272</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219793</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mossnycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza majalis subsp. sphagnicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älgmyra, V om, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626425.5407120861</v>
+        <v>626224</v>
       </c>
       <c r="R2" t="n">
-        <v>6897448.987590197</v>
+        <v>6897567</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,66 +740,52 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-08-12</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-08-12</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Fuktstråk i grov granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lage Sandgren</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lage Sandgren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Medelpads Flora (utgiven 2010)</t>
-        </is>
-      </c>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847868</v>
+        <v>119848312</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626244</v>
+        <v>626267</v>
       </c>
       <c r="R3" t="n">
-        <v>6897275</v>
+        <v>6897527</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847976</v>
+        <v>119848457</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626244</v>
+        <v>626418</v>
       </c>
       <c r="R4" t="n">
-        <v>6897275</v>
+        <v>6897386</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,50 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119848312</v>
+        <v>119847976</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626267</v>
+        <v>626244</v>
       </c>
       <c r="R5" t="n">
-        <v>6897527</v>
+        <v>6897275</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera bohål (&gt;10cm diamanter) i en ca 300-årig gammal tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,53 +1113,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119848457</v>
+        <v>120323464</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626418</v>
+        <v>626204</v>
       </c>
       <c r="R6" t="n">
-        <v>6897386</v>
+        <v>6897437</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,19 +1189,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:46</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flerhundraårig tall med flera bohål av spillkråka, i olika åldrar, enstaka färska, flera äldre. Adult fågel hördes i området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,15 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848186</v>
+        <v>119851155</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,37 +1234,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626224</v>
+        <v>626302</v>
       </c>
       <c r="R7" t="n">
-        <v>6897567</v>
+        <v>6897262</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,62 +1346,55 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848290</v>
+        <v>55593211</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99056</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219793</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mossnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza majalis subsp. sphagnicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Höppner) H. A. Pedersen &amp; Hedrén</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgmyran, Älgmyran, Mpd</t>
+          <t>Älgmyra, V om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626227</v>
+        <v>626426</v>
       </c>
       <c r="R8" t="n">
-        <v>6897562</v>
+        <v>6897449</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,98 +1418,98 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2009-08-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2009-08-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Fuktstråk i grov granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Lage Sandgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Lage Sandgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Medelpads Flora (utgiven 2010)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120323464</v>
+        <v>119848110</v>
       </c>
       <c r="B9" t="n">
-        <v>57681</v>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Galtström, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626204</v>
+        <v>626293</v>
       </c>
       <c r="R9" t="n">
-        <v>6897437</v>
+        <v>6897504</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,14 +1536,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flerhundraårig tall med flera bohål av spillkråka, i olika åldrar, enstaka färska, flera äldre. Adult fågel hördes i området.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,69 +1575,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119851155</v>
+        <v>119848290</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Älgmyrbäcken, Älgmyrbäcken, Mpd</t>
+          <t>Älgmyran, Älgmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626302</v>
+        <v>626227</v>
       </c>
       <c r="R10" t="n">
-        <v>6897262</v>
+        <v>6897562</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 33777-2024 artfynd.xlsx
+++ b/artfynd/A 33777-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848457</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119847976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120323464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851155</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
           <t>Medelpads Flora (utgiven 2010)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55593211</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848110</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,8 +1733,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119848290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>